--- a/data/nzd0152/nzd0152.xlsx
+++ b/data/nzd0152/nzd0152.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O340"/>
+  <dimension ref="A1:O344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17792,6 +17792,210 @@
         <v>326.77</v>
       </c>
       <c r="O340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>324.27</v>
+      </c>
+      <c r="C341" t="n">
+        <v>326</v>
+      </c>
+      <c r="D341" t="n">
+        <v>336.79</v>
+      </c>
+      <c r="E341" t="n">
+        <v>336.11</v>
+      </c>
+      <c r="F341" t="n">
+        <v>338.83</v>
+      </c>
+      <c r="G341" t="n">
+        <v>342.49</v>
+      </c>
+      <c r="H341" t="n">
+        <v>341.76</v>
+      </c>
+      <c r="I341" t="n">
+        <v>343.29</v>
+      </c>
+      <c r="J341" t="n">
+        <v>332.66</v>
+      </c>
+      <c r="K341" t="n">
+        <v>327.97</v>
+      </c>
+      <c r="L341" t="n">
+        <v>325.44</v>
+      </c>
+      <c r="M341" t="n">
+        <v>331.79</v>
+      </c>
+      <c r="N341" t="n">
+        <v>326.56</v>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>323.84</v>
+      </c>
+      <c r="C342" t="n">
+        <v>325.68</v>
+      </c>
+      <c r="D342" t="n">
+        <v>336.44</v>
+      </c>
+      <c r="E342" t="n">
+        <v>335.85</v>
+      </c>
+      <c r="F342" t="n">
+        <v>337.75</v>
+      </c>
+      <c r="G342" t="n">
+        <v>341.51</v>
+      </c>
+      <c r="H342" t="n">
+        <v>341.13</v>
+      </c>
+      <c r="I342" t="n">
+        <v>341.91</v>
+      </c>
+      <c r="J342" t="n">
+        <v>331.87</v>
+      </c>
+      <c r="K342" t="n">
+        <v>326.52</v>
+      </c>
+      <c r="L342" t="n">
+        <v>324.27</v>
+      </c>
+      <c r="M342" t="n">
+        <v>330.02</v>
+      </c>
+      <c r="N342" t="n">
+        <v>325.05</v>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>325.79</v>
+      </c>
+      <c r="C343" t="n">
+        <v>326.38</v>
+      </c>
+      <c r="D343" t="n">
+        <v>337.52</v>
+      </c>
+      <c r="E343" t="n">
+        <v>336.43</v>
+      </c>
+      <c r="F343" t="n">
+        <v>338.89</v>
+      </c>
+      <c r="G343" t="n">
+        <v>342.34</v>
+      </c>
+      <c r="H343" t="n">
+        <v>342.31</v>
+      </c>
+      <c r="I343" t="n">
+        <v>343.24</v>
+      </c>
+      <c r="J343" t="n">
+        <v>332.9</v>
+      </c>
+      <c r="K343" t="n">
+        <v>327.64</v>
+      </c>
+      <c r="L343" t="n">
+        <v>324.59</v>
+      </c>
+      <c r="M343" t="n">
+        <v>330.68</v>
+      </c>
+      <c r="N343" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>325.83</v>
+      </c>
+      <c r="C344" t="n">
+        <v>326.89</v>
+      </c>
+      <c r="D344" t="n">
+        <v>337.84</v>
+      </c>
+      <c r="E344" t="n">
+        <v>336.82</v>
+      </c>
+      <c r="F344" t="n">
+        <v>338.98</v>
+      </c>
+      <c r="G344" t="n">
+        <v>342.73</v>
+      </c>
+      <c r="H344" t="n">
+        <v>342.77</v>
+      </c>
+      <c r="I344" t="n">
+        <v>343.64</v>
+      </c>
+      <c r="J344" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="K344" t="n">
+        <v>327.56</v>
+      </c>
+      <c r="L344" t="n">
+        <v>324.76</v>
+      </c>
+      <c r="M344" t="n">
+        <v>330.53</v>
+      </c>
+      <c r="N344" t="n">
+        <v>324.75</v>
+      </c>
+      <c r="O344" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17808,7 +18012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B350"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21311,6 +21515,46 @@
       </c>
       <c r="B350" t="n">
         <v>-0.64</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -21479,28 +21723,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03178028165975938</v>
+        <v>0.01489970550762733</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001324191963844368</v>
+        <v>0.0002940970434317514</v>
       </c>
       <c r="M2" t="n">
-        <v>5.397688422082291</v>
+        <v>5.422385031618773</v>
       </c>
       <c r="N2" t="n">
-        <v>42.98849384304788</v>
+        <v>43.14708074215626</v>
       </c>
       <c r="O2" t="n">
-        <v>6.556561129361023</v>
+        <v>6.568643752111714</v>
       </c>
       <c r="P2" t="n">
-        <v>331.6898116808533</v>
+        <v>331.8686593605935</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21557,28 +21801,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06764514366519009</v>
+        <v>0.05753190737370129</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009008634935286364</v>
+        <v>0.006639757815373626</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1653751244334</v>
+        <v>4.156081986460684</v>
       </c>
       <c r="N3" t="n">
-        <v>28.4084339299686</v>
+        <v>28.3130418220447</v>
       </c>
       <c r="O3" t="n">
-        <v>5.329956278429364</v>
+        <v>5.32100007724532</v>
       </c>
       <c r="P3" t="n">
-        <v>328.985080448721</v>
+        <v>329.0922307518622</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21635,28 +21879,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1161085118539992</v>
+        <v>0.101510396528447</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02982881635611867</v>
+        <v>0.02307129046479695</v>
       </c>
       <c r="M4" t="n">
-        <v>3.973944438827752</v>
+        <v>3.998409108319989</v>
       </c>
       <c r="N4" t="n">
-        <v>24.74592155934883</v>
+        <v>24.94746858083397</v>
       </c>
       <c r="O4" t="n">
-        <v>4.974527269937198</v>
+        <v>4.994744095630323</v>
       </c>
       <c r="P4" t="n">
-        <v>340.6236269914633</v>
+        <v>340.7782968132114</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21713,28 +21957,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1517204944040896</v>
+        <v>0.1413867764860137</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04983085328145032</v>
+        <v>0.04417929705520196</v>
       </c>
       <c r="M5" t="n">
-        <v>4.020750219530814</v>
+        <v>4.017579366958199</v>
       </c>
       <c r="N5" t="n">
-        <v>24.77161163281284</v>
+        <v>24.72803847127107</v>
       </c>
       <c r="O5" t="n">
-        <v>4.977108762405423</v>
+        <v>4.972729478995522</v>
       </c>
       <c r="P5" t="n">
-        <v>336.9036906857561</v>
+        <v>337.0131792649661</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21791,28 +22035,28 @@
         <v>0.1704</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005834506323085473</v>
+        <v>-0.009762354023513753</v>
       </c>
       <c r="J6" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K6" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L6" t="n">
-        <v>7.030122244433556e-05</v>
+        <v>0.0001976373647388785</v>
       </c>
       <c r="M6" t="n">
-        <v>4.298171081192312</v>
+        <v>4.327386477778322</v>
       </c>
       <c r="N6" t="n">
-        <v>27.32612081231033</v>
+        <v>27.56567682358563</v>
       </c>
       <c r="O6" t="n">
-        <v>5.227439221292805</v>
+        <v>5.250302545909677</v>
       </c>
       <c r="P6" t="n">
-        <v>345.4826749143849</v>
+        <v>345.6479350310391</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21869,28 +22113,28 @@
         <v>0.1918</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04927109125179817</v>
+        <v>0.03103013729412136</v>
       </c>
       <c r="J7" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K7" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005592067926170508</v>
+        <v>0.002211288180028803</v>
       </c>
       <c r="M7" t="n">
-        <v>3.943226910117837</v>
+        <v>3.989962074910149</v>
       </c>
       <c r="N7" t="n">
-        <v>24.36349941952754</v>
+        <v>24.84134384907083</v>
       </c>
       <c r="O7" t="n">
-        <v>4.935939568058703</v>
+        <v>4.984109132941496</v>
       </c>
       <c r="P7" t="n">
-        <v>349.1706816421606</v>
+        <v>349.3639588677526</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21947,28 +22191,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04088882892909437</v>
+        <v>0.01912482086116367</v>
       </c>
       <c r="J8" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K8" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002759390137484496</v>
+        <v>0.0006007772274511103</v>
       </c>
       <c r="M8" t="n">
-        <v>4.731751149501934</v>
+        <v>4.772031630038247</v>
       </c>
       <c r="N8" t="n">
-        <v>34.10039082368623</v>
+        <v>34.78842338680055</v>
       </c>
       <c r="O8" t="n">
-        <v>5.839553991846143</v>
+        <v>5.898171190021577</v>
       </c>
       <c r="P8" t="n">
-        <v>350.7077507753399</v>
+        <v>350.9383505943113</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22025,28 +22269,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05471556664034791</v>
+        <v>0.03771213854928496</v>
       </c>
       <c r="J9" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K9" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00383032479639589</v>
+        <v>0.001840724191328968</v>
       </c>
       <c r="M9" t="n">
-        <v>5.347128465552373</v>
+        <v>5.357481925876887</v>
       </c>
       <c r="N9" t="n">
-        <v>43.94228952638224</v>
+        <v>44.09485294479523</v>
       </c>
       <c r="O9" t="n">
-        <v>6.628898062753887</v>
+        <v>6.640395541290837</v>
       </c>
       <c r="P9" t="n">
-        <v>349.2196111351453</v>
+        <v>349.399773081023</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22103,28 +22347,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1017520486290474</v>
+        <v>0.0792092583144182</v>
       </c>
       <c r="J10" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K10" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01251823115222883</v>
+        <v>0.007619950189432068</v>
       </c>
       <c r="M10" t="n">
-        <v>5.493615379166401</v>
+        <v>5.54446383636599</v>
       </c>
       <c r="N10" t="n">
-        <v>46.09306704884158</v>
+        <v>46.71885991316915</v>
       </c>
       <c r="O10" t="n">
-        <v>6.789187510213692</v>
+        <v>6.835119597576121</v>
       </c>
       <c r="P10" t="n">
-        <v>340.127902198702</v>
+        <v>340.3667574392704</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22181,28 +22425,28 @@
         <v>0.1989</v>
       </c>
       <c r="I11" t="n">
-        <v>0.087905626384136</v>
+        <v>0.06428146325092311</v>
       </c>
       <c r="J11" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K11" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007001681402518334</v>
+        <v>0.003771519089543873</v>
       </c>
       <c r="M11" t="n">
-        <v>6.458717626678385</v>
+        <v>6.491894417229399</v>
       </c>
       <c r="N11" t="n">
-        <v>61.85042348287269</v>
+        <v>62.40632401805403</v>
       </c>
       <c r="O11" t="n">
-        <v>7.864504020144734</v>
+        <v>7.899767339488805</v>
       </c>
       <c r="P11" t="n">
-        <v>335.7158573716239</v>
+        <v>335.9661802632812</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22259,28 +22503,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1027648284537485</v>
+        <v>0.07410752424211216</v>
       </c>
       <c r="J12" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K12" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L12" t="n">
-        <v>0.008008426690882642</v>
+        <v>0.004178065454689683</v>
       </c>
       <c r="M12" t="n">
-        <v>6.963201244173126</v>
+        <v>7.0149420988254</v>
       </c>
       <c r="N12" t="n">
-        <v>73.82661319252293</v>
+        <v>74.84202130176523</v>
       </c>
       <c r="O12" t="n">
-        <v>8.592241453341668</v>
+        <v>8.651128325355325</v>
       </c>
       <c r="P12" t="n">
-        <v>334.9274966325081</v>
+        <v>335.2311554554898</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22337,28 +22581,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1488647364368933</v>
+        <v>0.1229630727388578</v>
       </c>
       <c r="J13" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K13" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02033042320241474</v>
+        <v>0.01395146567322436</v>
       </c>
       <c r="M13" t="n">
-        <v>6.385077402994115</v>
+        <v>6.452588388026564</v>
       </c>
       <c r="N13" t="n">
-        <v>60.26706360241457</v>
+        <v>61.10015636486023</v>
       </c>
       <c r="O13" t="n">
-        <v>7.763186433573173</v>
+        <v>7.816658900378104</v>
       </c>
       <c r="P13" t="n">
-        <v>338.44471970599</v>
+        <v>338.7191839143497</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22415,28 +22659,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1133965034580159</v>
+        <v>0.08328701721578763</v>
       </c>
       <c r="J14" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K14" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01096572923292027</v>
+        <v>0.00590524839119444</v>
       </c>
       <c r="M14" t="n">
-        <v>6.702378560884913</v>
+        <v>6.792905769444281</v>
       </c>
       <c r="N14" t="n">
-        <v>65.45401823438975</v>
+        <v>66.76651049856196</v>
       </c>
       <c r="O14" t="n">
-        <v>8.090365766415617</v>
+        <v>8.171077682812834</v>
       </c>
       <c r="P14" t="n">
-        <v>335.7706751806921</v>
+        <v>336.0897336357679</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22474,7 +22718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O340"/>
+  <dimension ref="A1:O344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48657,6 +48901,314 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-36.69364142750095,175.6040414045994</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-36.694361018713906,175.60418928378687</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-36.69507347683047,175.6044946809875</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-36.69575849361012,175.60487401355354</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-36.696396190421574,175.6053173909895</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-36.697007967428505,175.60581650897362</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-36.69761617494351,175.6063211371207</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-36.69818698746387,175.60689697167635</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-36.69876160016449,175.607478349095</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-36.69929040094346,175.60809864302874</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-36.69979731720201,175.60875776175067</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-36.70022777029221,175.60953616863165</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>-36.700601811895815,175.61034797995237</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-36.69364204230705,175.60403665525874</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-36.694361559659804,175.60418576757627</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-36.69507450479194,175.60449097947023</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-36.695759551568244,175.60487141851556</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-36.69640104054776,175.60530691706447</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-36.697012822373104,175.60580735196277</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-36.697619589258665,175.60631550707194</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-36.69819549348233,175.6068857122388</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-36.698766848361515,175.60747237949718</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-36.69930014483543,175.60808783869982</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-36.69980544304742,175.60874942471781</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-36.70024134787733,175.60952578494982</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-36.70061412219101,175.61034079130224</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-36.6936392542314,175.60405819296562</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-36.694360376340505,175.60419345928688</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-36.69507133279618,175.6045024012946</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-36.69575719150777,175.6048772074463</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-36.69639592097009,175.6053179728742</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-36.697008710532316,175.60581510739038</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-36.697613194192,175.6063260522422</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-36.69818729565296,175.60689656372577</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-36.69876000577546,175.60748016264355</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-36.69929261851895,175.60809618411275</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-36.69980322059402,175.6087517049321</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-36.70023628504908,175.6095296568316</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-36.700617790821966,175.61033864898886</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-36.693639197040056,175.60405863476473</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-36.69435951420756,175.60419906324728</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-36.69507039294538,175.60450578553872</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-36.69575560457038,175.60488110000296</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-36.696395516792876,175.60531884570122</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-36.69700677846239,175.6058187515067</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-36.697610701199665,175.60633016307077</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-36.698184830140185,175.6068998273304</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-36.698757082728875,175.60748348748234</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-36.699293156113015,175.60809558801188</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-36.69980203991565,175.60875291629588</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-36.70023743569187,175.6095287768585</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-36.70061656794499,175.61033936309335</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0152/nzd0152.xlsx
+++ b/data/nzd0152/nzd0152.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O344"/>
+  <dimension ref="A1:O345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17998,6 +17998,57 @@
       <c r="O344" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>328.03</v>
+      </c>
+      <c r="C345" t="n">
+        <v>327.72</v>
+      </c>
+      <c r="D345" t="n">
+        <v>338.61</v>
+      </c>
+      <c r="E345" t="n">
+        <v>337.38</v>
+      </c>
+      <c r="F345" t="n">
+        <v>339.81</v>
+      </c>
+      <c r="G345" t="n">
+        <v>344.02</v>
+      </c>
+      <c r="H345" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="I345" t="n">
+        <v>344.82</v>
+      </c>
+      <c r="J345" t="n">
+        <v>334.29</v>
+      </c>
+      <c r="K345" t="n">
+        <v>328.53</v>
+      </c>
+      <c r="L345" t="n">
+        <v>325.13</v>
+      </c>
+      <c r="M345" t="n">
+        <v>331.17</v>
+      </c>
+      <c r="N345" t="n">
+        <v>324.57</v>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21555,6 +21606,16 @@
       </c>
       <c r="B354" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -21723,28 +21784,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01489970550762733</v>
+        <v>0.01255745967571965</v>
       </c>
       <c r="J2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002940970434317514</v>
+        <v>0.00020993590193219</v>
       </c>
       <c r="M2" t="n">
-        <v>5.422385031618773</v>
+        <v>5.418680120072328</v>
       </c>
       <c r="N2" t="n">
-        <v>43.14708074215626</v>
+        <v>43.07339250349862</v>
       </c>
       <c r="O2" t="n">
-        <v>6.568643752111714</v>
+        <v>6.563032264395675</v>
       </c>
       <c r="P2" t="n">
-        <v>331.8686593605935</v>
+        <v>331.8935394877281</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21801,28 +21862,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05753190737370129</v>
+        <v>0.05592076294338037</v>
       </c>
       <c r="J3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006639757815373626</v>
+        <v>0.006307870497687773</v>
       </c>
       <c r="M3" t="n">
-        <v>4.156081986460684</v>
+        <v>4.150261031856044</v>
       </c>
       <c r="N3" t="n">
-        <v>28.3130418220447</v>
+        <v>28.25521721850268</v>
       </c>
       <c r="O3" t="n">
-        <v>5.32100007724532</v>
+        <v>5.31556367834143</v>
       </c>
       <c r="P3" t="n">
-        <v>329.0922307518622</v>
+        <v>329.1093448727254</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21879,28 +21940,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.101510396528447</v>
+        <v>0.09880906349601185</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02307129046479695</v>
+        <v>0.02195699380986449</v>
       </c>
       <c r="M4" t="n">
-        <v>3.998409108319989</v>
+        <v>4.000057238463743</v>
       </c>
       <c r="N4" t="n">
-        <v>24.94746858083397</v>
+        <v>24.94376645324146</v>
       </c>
       <c r="O4" t="n">
-        <v>4.994744095630323</v>
+        <v>4.994373479550909</v>
       </c>
       <c r="P4" t="n">
-        <v>340.7782968132114</v>
+        <v>340.8069912859966</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21957,28 +22018,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1413867764860137</v>
+        <v>0.1394971530512472</v>
       </c>
       <c r="J5" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K5" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04417929705520196</v>
+        <v>0.0432507955163699</v>
       </c>
       <c r="M5" t="n">
-        <v>4.017579366958199</v>
+        <v>4.013933349500181</v>
       </c>
       <c r="N5" t="n">
-        <v>24.72803847127107</v>
+        <v>24.68982953840662</v>
       </c>
       <c r="O5" t="n">
-        <v>4.972729478995522</v>
+        <v>4.968886146653656</v>
       </c>
       <c r="P5" t="n">
-        <v>337.0131792649661</v>
+        <v>337.0332514839677</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22035,28 +22096,28 @@
         <v>0.1704</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.009762354023513753</v>
+        <v>-0.01284447950055411</v>
       </c>
       <c r="J6" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K6" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001976373647388785</v>
+        <v>0.0003430439647965633</v>
       </c>
       <c r="M6" t="n">
-        <v>4.327386477778322</v>
+        <v>4.33065475299754</v>
       </c>
       <c r="N6" t="n">
-        <v>27.56567682358563</v>
+        <v>27.57513339746368</v>
       </c>
       <c r="O6" t="n">
-        <v>5.250302545909677</v>
+        <v>5.251203042871574</v>
       </c>
       <c r="P6" t="n">
-        <v>345.6479350310391</v>
+        <v>345.6806744099159</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22113,28 +22174,28 @@
         <v>0.1918</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03103013729412136</v>
+        <v>0.02761524361480852</v>
       </c>
       <c r="J7" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K7" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002211288180028803</v>
+        <v>0.001755025565897017</v>
       </c>
       <c r="M7" t="n">
-        <v>3.989962074910149</v>
+        <v>3.996186420671241</v>
       </c>
       <c r="N7" t="n">
-        <v>24.84134384907083</v>
+        <v>24.87910973839661</v>
       </c>
       <c r="O7" t="n">
-        <v>4.984109132941496</v>
+        <v>4.98789632394225</v>
       </c>
       <c r="P7" t="n">
-        <v>349.3639588677526</v>
+        <v>349.4002330229821</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22191,28 +22252,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01912482086116367</v>
+        <v>0.01480460463468168</v>
       </c>
       <c r="J8" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K8" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006007772274511103</v>
+        <v>0.0003604555808859322</v>
       </c>
       <c r="M8" t="n">
-        <v>4.772031630038247</v>
+        <v>4.77723964495627</v>
       </c>
       <c r="N8" t="n">
-        <v>34.78842338680055</v>
+        <v>34.86331616679447</v>
       </c>
       <c r="O8" t="n">
-        <v>5.898171190021577</v>
+        <v>5.904516590441124</v>
       </c>
       <c r="P8" t="n">
-        <v>350.9383505943113</v>
+        <v>350.9842413917245</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22269,28 +22330,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03771213854928496</v>
+        <v>0.03462403484986898</v>
       </c>
       <c r="J9" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K9" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001840724191328968</v>
+        <v>0.001558297614285387</v>
       </c>
       <c r="M9" t="n">
-        <v>5.357481925876887</v>
+        <v>5.355170975163697</v>
       </c>
       <c r="N9" t="n">
-        <v>44.09485294479523</v>
+        <v>44.05660746783209</v>
       </c>
       <c r="O9" t="n">
-        <v>6.640395541290837</v>
+        <v>6.637515157634828</v>
       </c>
       <c r="P9" t="n">
-        <v>349.399773081023</v>
+        <v>349.4325759625991</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22347,28 +22408,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0792092583144182</v>
+        <v>0.07467971581770537</v>
       </c>
       <c r="J10" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K10" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007619950189432068</v>
+        <v>0.00679204855219584</v>
       </c>
       <c r="M10" t="n">
-        <v>5.54446383636599</v>
+        <v>5.551720814052</v>
       </c>
       <c r="N10" t="n">
-        <v>46.71885991316915</v>
+        <v>46.7765419173863</v>
       </c>
       <c r="O10" t="n">
-        <v>6.835119597576121</v>
+        <v>6.839337827405976</v>
       </c>
       <c r="P10" t="n">
-        <v>340.3667574392704</v>
+        <v>340.4148717710986</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22425,28 +22486,28 @@
         <v>0.1989</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06428146325092311</v>
+        <v>0.05922111122406642</v>
       </c>
       <c r="J11" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K11" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003771519089543873</v>
+        <v>0.003209915919729966</v>
       </c>
       <c r="M11" t="n">
-        <v>6.491894417229399</v>
+        <v>6.497419985576257</v>
       </c>
       <c r="N11" t="n">
-        <v>62.40632401805403</v>
+        <v>62.46641034407732</v>
       </c>
       <c r="O11" t="n">
-        <v>7.899767339488805</v>
+        <v>7.90356946854251</v>
       </c>
       <c r="P11" t="n">
-        <v>335.9661802632812</v>
+        <v>336.0199330334041</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22503,28 +22564,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07410752424211216</v>
+        <v>0.06743012766908726</v>
       </c>
       <c r="J12" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K12" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004178065454689683</v>
+        <v>0.003463085467155347</v>
       </c>
       <c r="M12" t="n">
-        <v>7.0149420988254</v>
+        <v>7.026131679802909</v>
       </c>
       <c r="N12" t="n">
-        <v>74.84202130176523</v>
+        <v>75.04496127593788</v>
       </c>
       <c r="O12" t="n">
-        <v>8.651128325355325</v>
+        <v>8.662849489396539</v>
       </c>
       <c r="P12" t="n">
-        <v>335.2311554554898</v>
+        <v>335.3020850195013</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22581,28 +22642,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1229630727388578</v>
+        <v>0.1169686943605272</v>
       </c>
       <c r="J13" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K13" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01395146567322436</v>
+        <v>0.01264759123706594</v>
       </c>
       <c r="M13" t="n">
-        <v>6.452588388026564</v>
+        <v>6.466893700420125</v>
       </c>
       <c r="N13" t="n">
-        <v>61.10015636486023</v>
+        <v>61.26141818654074</v>
       </c>
       <c r="O13" t="n">
-        <v>7.816658900378104</v>
+        <v>7.826967368434644</v>
       </c>
       <c r="P13" t="n">
-        <v>338.7191839143497</v>
+        <v>338.7828582281703</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22659,28 +22720,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08328701721578763</v>
+        <v>0.07568459153542435</v>
       </c>
       <c r="J14" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K14" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00590524839119444</v>
+        <v>0.004871265717485418</v>
       </c>
       <c r="M14" t="n">
-        <v>6.792905769444281</v>
+        <v>6.815704420811265</v>
       </c>
       <c r="N14" t="n">
-        <v>66.76651049856196</v>
+        <v>67.1175016798118</v>
       </c>
       <c r="O14" t="n">
-        <v>8.171077682812834</v>
+        <v>8.192527185173804</v>
       </c>
       <c r="P14" t="n">
-        <v>336.0897336357679</v>
+        <v>336.1704891717079</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22718,7 +22779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O344"/>
+  <dimension ref="A1:O345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49209,6 +49270,83 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-36.69363605151411,175.60408293371393</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-36.694358111127904,175.60420818341785</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-36.69506813142902,175.60451392887566</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-36.69575332589088,175.6048866893148</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-36.69639178938039,175.60532689510552</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-36.69700038776877,175.60583080512083</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-36.69760604038758,175.6063378485322</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-36.69817755687704,175.60690945496287</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-36.69875077160524,175.6074906661107</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-36.699286637784944,175.60810281573438</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-36.69979947020383,175.6087555527934</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-36.70023252628257,175.60953253141017</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-36.70061803539735,175.61033850616795</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
